--- a/data/output/default/pureComponents_filled.xlsx
+++ b/data/output/default/pureComponents_filled.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,18 +491,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>228.3073440249161</v>
+        <v>207.6343091879377</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>8.161131425851703</v>
+        <v>5.666543518127263</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="n">
-        <v>43.86210910925365</v>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
     </row>
@@ -519,18 +517,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>196.0432816049791</v>
+        <v>278.3738322189085</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>5.659337598535998</v>
+        <v>8.183163166750072</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="n">
-        <v>-42.53048822177161</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
     </row>
@@ -547,18 +543,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>262.0070459883168</v>
+        <v>300.3752346525182</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>10.96926928910882</v>
+        <v>17.628222033811</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>120.0051387245415</v>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
     </row>
@@ -575,18 +569,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>153.1986710687383</v>
+        <v>211.2627441509854</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>2.171286881361082</v>
+        <v>4.549359601872325</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="n">
-        <v>-51.72811126648988</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
     </row>
@@ -603,18 +595,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>194.8659659111482</v>
+        <v>260.2088239930473</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>8.100258058557745</v>
+        <v>10.62329022842948</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
-        <v>-2.424218468020939</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
     </row>
@@ -631,18 +621,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>231.3306761821181</v>
+        <v>385.337424027835</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>6.934035389394992</v>
+        <v>22.58337040941969</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>-145.7948982613383</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
     </row>
@@ -659,18 +647,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>690.0820400038931</v>
+        <v>394.306896904131</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>15.96172525146676</v>
+        <v>-30.08976092782388</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>-289.0536250569793</v>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
     </row>
@@ -687,18 +673,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>93.15136791441068</v>
+        <v>226.9673992903919</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>1.119321965225947</v>
+        <v>5.227876854604808</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>-51.92289686485732</v>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
     </row>
@@ -715,18 +699,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>523.7755248889397</v>
+        <v>439.9326733251125</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>13.97228339408038</v>
+        <v>58.82644812374284</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="n">
-        <v>-284.8251085526556</v>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
     </row>
@@ -743,18 +725,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>245.3395075433034</v>
+        <v>232.1663908969329</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>8.110577414704128</v>
+        <v>7.544641580436769</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
-        <v>183.1125994005462</v>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
     </row>
@@ -771,18 +751,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>172.7187372093812</v>
+        <v>262.6810604770972</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>6.41214952612307</v>
+        <v>10.95815124709674</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="n">
-        <v>5.494580656579188</v>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
     </row>
@@ -799,18 +777,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.61794002521016</v>
+        <v>-67.5334096573081</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>0.1092176459520076</v>
+        <v>-0.636078365181568</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
-        <v>1.517316586476056</v>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
     </row>
@@ -827,18 +803,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>174.0830287782407</v>
+        <v>217.4590406412959</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>5.895450425848606</v>
+        <v>6.347339238178552</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
-        <v>-12.416299910801</v>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
     </row>
@@ -855,18 +829,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>215.2204896811633</v>
+        <v>246.5293682018625</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>10.06127428792409</v>
+        <v>8.971669423100268</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>23.21437345378052</v>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
     </row>
@@ -883,18 +855,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>63.13392826701418</v>
+        <v>165.1569259713358</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>0.7157032701772934</v>
+        <v>3.504053317130499</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="n">
-        <v>2.021520457057761</v>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
     </row>
@@ -911,18 +881,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>264.1140528256768</v>
+        <v>288.4369837993383</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>14.65223687538459</v>
+        <v>15.16885555356915</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="n">
-        <v>54.59480557343034</v>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
     </row>
@@ -939,18 +907,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>72.29570329092701</v>
+        <v>180.2919827538946</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>0.7829678331947871</v>
+        <v>4.15762531287141</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="n">
-        <v>-39.04713406810353</v>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
     </row>
@@ -967,18 +933,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>97.41126693705461</v>
+        <v>173.2915801578876</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>2.841652299474156</v>
+        <v>3.842021671583382</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="n">
-        <v>-55.70272689207954</v>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
     </row>
@@ -995,18 +959,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>176.3511191482272</v>
+        <v>306.3383408429013</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>6.633907343573254</v>
+        <v>18.99552621957993</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="n">
-        <v>-78.59055939209235</v>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
     </row>
@@ -1023,18 +985,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>135.101650527461</v>
+        <v>253.4893125094072</v>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>4.456062752973631</v>
+        <v>9.772373860387235</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
-        <v>-98.97168913076459</v>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
     </row>
@@ -1051,18 +1011,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>199.4557867963873</v>
+        <v>345.5359419654188</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
-        <v>8.902215581230417</v>
+        <v>30.79922701031169</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="n">
-        <v>-62.84058467976675</v>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
     </row>
@@ -1079,18 +1037,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>180.9296444689634</v>
+        <v>180.5044495427356</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>5.502719023952096</v>
+        <v>4.167203348488052</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
-        <v>37.11142392704386</v>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
     </row>
@@ -1107,18 +1063,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>143.9359968080012</v>
+        <v>146.029715532268</v>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>3.121453109632217</v>
+        <v>2.447920168282014</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="n">
-        <v>-93.03572544567713</v>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
     </row>
@@ -1135,18 +1089,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>915.802056718202</v>
+        <v>837.6245928598424</v>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>19.95897233329273</v>
+        <v>20.04603871925838</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="n">
-        <v>-384.4495345555417</v>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
     </row>
@@ -1163,18 +1115,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>86.51300017173428</v>
+        <v>269.7402650642909</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
-        <v>0.9255970443938928</v>
+        <v>7.589682292924023</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
-        <v>-61.36757480909552</v>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
     </row>
@@ -1191,18 +1141,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>174.4193709347202</v>
+        <v>291.6566492059454</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>5.944460596312863</v>
+        <v>15.79815551770654</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
-        <v>-63.82688040777535</v>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
     </row>
@@ -1219,18 +1167,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>178.9125280786299</v>
+        <v>229.1083715077178</v>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>6.427222286478615</v>
+        <v>7.275509831188712</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
-        <v>-92.49856593063073</v>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
     </row>
@@ -1247,18 +1193,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>209.6132286084546</v>
+        <v>335.422165097185</v>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
-        <v>9.134197957592045</v>
+        <v>27.24263852939092</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="n">
-        <v>-45.48515288577121</v>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
     </row>
@@ -1275,18 +1219,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>177.7103035541482</v>
+        <v>176.9996875916552</v>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>6.118061418413255</v>
+        <v>4.005345598146373</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="n">
-        <v>-14.96687690389288</v>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
     </row>
@@ -1303,18 +1245,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>222.9720070458304</v>
+        <v>219.7357844868837</v>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>10.4368609327585</v>
+        <v>6.51721122562946</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="n">
-        <v>44.15571167036396</v>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
     </row>
@@ -1331,18 +1271,16 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>237.699660591148</v>
+        <v>382.9287977155892</v>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>8.003510709069861</v>
+        <v>21.97647084583947</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="n">
-        <v>-156.0113854059831</v>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
     </row>
@@ -1359,18 +1297,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1067.60834439781</v>
+        <v>818.8886461031274</v>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>26.35559181291319</v>
+        <v>24.71975608877753</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="n">
-        <v>-420.3546217511738</v>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
     </row>
@@ -1387,18 +1323,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>694.8467976198772</v>
+        <v>387.6626204147572</v>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>15.94844009611295</v>
+        <v>-24.22931458454706</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="n">
-        <v>-289.3116859924255</v>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
     </row>
@@ -1415,18 +1349,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>177.2676240237559</v>
+        <v>237.8380919334203</v>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>5.016937364730383</v>
+        <v>8.075957319250964</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="n">
-        <v>20.12538767936229</v>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
     </row>
@@ -1443,18 +1375,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>193.8453805002812</v>
+        <v>244.9059207489362</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>10.90063609101187</v>
+        <v>8.794930720884199</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="n">
-        <v>-64.15985984202919</v>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
     </row>
@@ -1471,18 +1401,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>779.2662381669983</v>
+        <v>483.2878224493667</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>17.2304914439109</v>
+        <v>41.20308730457428</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="n">
-        <v>-346.5899078016376</v>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
     </row>
@@ -1499,18 +1427,16 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>196.8065584910799</v>
+        <v>320.2723131887454</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>5.518712671732779</v>
+        <v>11.85974002837583</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
-        <v>-123.8281372968587</v>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
     </row>
@@ -1527,18 +1453,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1023.648911999597</v>
+        <v>816.513554086742</v>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>30.29092381586571</v>
+        <v>27.54347219508262</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="n">
-        <v>-428.7999366421153</v>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
     </row>
@@ -1555,18 +1479,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>695.3193316898694</v>
+        <v>378.9571359402014</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>15.72539574476</v>
+        <v>-18.63414298925267</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="n">
-        <v>-287.8259585910245</v>
-      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
     </row>
@@ -1583,18 +1505,16 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>394.5351511663545</v>
+        <v>420.7095250891575</v>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>13.87836641917858</v>
+        <v>14.10725279380458</v>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="n">
-        <v>-477.4338979053063</v>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
     </row>
@@ -1611,18 +1531,16 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>329.2530052851508</v>
+        <v>375.199722870713</v>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>19.97305649391247</v>
+        <v>21.46676578012656</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="n">
-        <v>-543.7687380742204</v>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
     </row>
@@ -1639,18 +1557,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>417.4857091246428</v>
+        <v>420.2189282426566</v>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>9.620954674087432</v>
+        <v>10.25403761514374</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="n">
-        <v>-468.7404287605186</v>
-      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
     </row>
@@ -1667,18 +1583,16 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>389.1954838280193</v>
+        <v>427.3839743498265</v>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>14.94767922930784</v>
+        <v>122.3018878788312</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="n">
-        <v>-576.0036558366829</v>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
     </row>
@@ -1695,18 +1609,16 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>361.3565522561348</v>
+        <v>425.7093236555233</v>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>11.22240329851656</v>
+        <v>160.4245915363377</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="n">
-        <v>-240.1020940590974</v>
-      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
     </row>
@@ -1723,18 +1635,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>539.5540163123043</v>
+        <v>440.7142670495214</v>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>17.09545955396917</v>
+        <v>43.28613875171057</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="n">
-        <v>-352.9057233918021</v>
-      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
     </row>
@@ -1751,18 +1661,16 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>530.4283259309605</v>
+        <v>490.4621106731292</v>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>51.23247095407484</v>
+        <v>49.68132498153454</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="n">
-        <v>-400.2861833623692</v>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
     </row>
@@ -1779,18 +1687,16 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>548.693482942535</v>
+        <v>441.6909659258902</v>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>15.42980442375327</v>
+        <v>41.38234208306964</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="n">
-        <v>-326.9792255631268</v>
-      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
     </row>
@@ -1807,18 +1713,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>567.225803324895</v>
+        <v>428.2263736626531</v>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>54.14493994561509</v>
+        <v>109.3125759355658</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="n">
-        <v>-424.3854043887093</v>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
     </row>
@@ -1835,18 +1739,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>349.5050121030861</v>
+        <v>458.5567158460356</v>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>11.87940421091175</v>
+        <v>23.94907084982593</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="n">
-        <v>-219.5924679140367</v>
-      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
     </row>
@@ -1863,18 +1765,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>373.4658420760145</v>
+        <v>409.6766667223462</v>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>13.74329982667764</v>
+        <v>14.6042892957258</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="n">
-        <v>-224.7131010846904</v>
-      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
     </row>
@@ -1891,18 +1791,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>527.7399982456692</v>
+        <v>532.1067248474651</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>13.25860918206162</v>
+        <v>9.505146666682949</v>
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="n">
-        <v>-244.9121502630621</v>
-      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
     </row>
@@ -1919,18 +1817,16 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>642.4928847813096</v>
+        <v>571.7308634853503</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>20.50283761260872</v>
+        <v>19.40239334437265</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="n">
-        <v>-286.3171447487703</v>
-      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
     </row>
@@ -1947,18 +1843,16 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>534.0756356121104</v>
+        <v>570.0174155880933</v>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>12.78664083421696</v>
+        <v>7.601082918202716</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="n">
-        <v>-223.3866894888038</v>
-      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
     </row>
@@ -1975,18 +1869,16 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>680.290292610294</v>
+        <v>435.6667532475254</v>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>37.18438914627166</v>
+        <v>56.92916820318108</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="n">
-        <v>-338.0171302721544</v>
-      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
     </row>
@@ -2003,18 +1895,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>377.4818951714212</v>
+        <v>408.9906292582096</v>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>40.78004826756622</v>
+        <v>41.46245314135322</v>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="n">
-        <v>-268.6043353500738</v>
-      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
     </row>
@@ -2031,18 +1921,16 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>292.215609822638</v>
+        <v>344.1519456730116</v>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>1.296078181003644</v>
+        <v>2.816160641073264</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="n">
-        <v>-204.0805159060272</v>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
     </row>
@@ -2059,18 +1947,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>410.5014288340435</v>
+        <v>415.2175599927775</v>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>39.30949938932008</v>
+        <v>38.88845369166702</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="n">
-        <v>-274.592118600453</v>
-      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
     </row>
@@ -2087,18 +1973,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>583.9180082621111</v>
+        <v>486.277920134422</v>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>7.304949884793045</v>
+        <v>8.151146740771523</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="n">
-        <v>-419.2400263762158</v>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
     </row>
@@ -2115,18 +1999,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>474.0472196475421</v>
+        <v>469.4500591428435</v>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>66.57873487488578</v>
+        <v>64.19932824781439</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="n">
-        <v>-484.8151127643249</v>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
     </row>
@@ -2143,18 +2025,16 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>607.234324998639</v>
+        <v>485.2890635902297</v>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>6.834850396722922</v>
+        <v>9.312873127468659</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="n">
-        <v>-397.9947791517127</v>
-      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
     </row>
@@ -2171,18 +2051,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>154.578084659032</v>
+        <v>244.9059207489362</v>
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>6.558462287022721</v>
+        <v>8.794930720884199</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="n">
-        <v>-32.3547896211667</v>
-      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
     </row>
@@ -2199,18 +2077,16 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>564.9064803354956</v>
+        <v>663.8256417842998</v>
       </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>7.152570100857199</v>
+        <v>7.869523022763454</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="n">
-        <v>-184.3787496630463</v>
-      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
     </row>
@@ -2227,104 +2103,200 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>374.9980205196892</v>
+        <v>436.3681685247605</v>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>15.71148763614801</v>
+        <v>17.67700370597852</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="n">
-        <v>-426.6825552242536</v>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ammonia borane</t>
+          <t>tetraethylammonium borohydride</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[BH3-][NH3+]</t>
+          <t>CC[N+](CC)(CC)CC.[BH4-]</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>171.4914366875161</v>
+        <v>440.2362969840546</v>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>5.434383760022104</v>
+        <v>44.29258584079773</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="n">
-        <v>-92.76430985369848</v>
-      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>thiourea</t>
+          <t>tetramethylammonium borohydride</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>C(=S)(N)N</t>
+          <t>C[N+](C)(C)C.[BH4-]</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>222.786251595354</v>
+        <v>519.01506655898</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>11.44486722840647</v>
+        <v>10.50253330246275</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="n">
-        <v>2.559104722639347</v>
-      </c>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>thioacetamide</t>
+          <t>ammonia borane</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CC(=S)N</t>
+          <t>[BH3-][NH3+]</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>193.4307072006281</v>
+        <v>176.2653677361802</v>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>8.858635938082038</v>
+        <v>3.972852112316922</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="n">
-        <v>-4.196227730131795</v>
-      </c>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>thiourea</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>C(=S)(N)N</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>269.6304784882003</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="n">
+        <v>11.95615400843688</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>thioacetamide</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CC(=S)N</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>268.2975880029467</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="n">
+        <v>11.76218128886559</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>dimethylamine borane</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>[B].CNC</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>211.2627441509854</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="n">
+        <v>4.549359601872325</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>trimethylamine borane</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>[B].CN(C)C</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>211.2627441509854</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="n">
+        <v>4.549359601872325</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
